--- a/diseases/d122/2015-2019.xlsx
+++ b/diseases/d122/2015-2019.xlsx
@@ -1955,6 +1955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13605,6 +13610,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30091,6 +30101,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46577,6 +46592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62670,6 +62690,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73544,6 +73569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76513,6 +76543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76661,6 +76696,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77613,6 +77653,11 @@
       <c r="S390" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO390" t="inlineStr">
